--- a/public/demo-data.xlsx
+++ b/public/demo-data.xlsx
@@ -5,8 +5,24 @@
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
     <sheet name="People" sheetId="2" r:id="rId2"/>
-    <sheet name="Tasks" sheetId="3" r:id="rId3"/>
-    <sheet name="GoogleEvents" sheetId="4" r:id="rId4"/>
+    <sheet name="SubProjects" sheetId="3" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="4" r:id="rId4"/>
+    <sheet name="GoogleEvents" sheetId="5" r:id="rId5"/>
+    <sheet name="Briefing" sheetId="6" r:id="rId6"/>
+    <sheet name="PostIts" sheetId="7" r:id="rId7"/>
+    <sheet name="Partenaires" sheetId="8" r:id="rId8"/>
+    <sheet name="Suivis" sheetId="9" r:id="rId9"/>
+    <sheet name="Temps" sheetId="10" r:id="rId10"/>
+    <sheet name="Associations" sheetId="11" r:id="rId11"/>
+    <sheet name="Tickets" sheetId="12" r:id="rId12"/>
+    <sheet name="CAP_Clients" sheetId="13" r:id="rId13"/>
+    <sheet name="CAP_Projets" sheetId="14" r:id="rId14"/>
+    <sheet name="CAP_Taches" sheetId="15" r:id="rId15"/>
+    <sheet name="CAP_SousTaches" sheetId="16" r:id="rId16"/>
+    <sheet name="CAP_SuiviProjet" sheetId="17" r:id="rId17"/>
+    <sheet name="CAP_Echanges" sheetId="18" r:id="rId18"/>
+    <sheet name="CAP_Documents" sheetId="19" r:id="rId19"/>
+    <sheet name="CAP_TempsProjet" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -453,6 +469,2326 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>start</v>
+      </c>
+      <c r="D1" t="str">
+        <v>end</v>
+      </c>
+      <c r="E1" t="str">
+        <v>dureeH</v>
+      </c>
+      <c r="F1" t="str">
+        <v>dureeMin</v>
+      </c>
+      <c r="G1" t="str">
+        <v>commentaire</v>
+      </c>
+      <c r="H1" t="str">
+        <v>projets</v>
+      </c>
+      <c r="I1" t="str">
+        <v>sousProjets</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TM1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Coordination gestion matériel</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-06-02 09:00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-06-02 11:00</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Réunion mensuelle équipe</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Gestion administrative CUMA</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TM2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Préparation dossier PCAE</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-06-03 14:00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-03 17:30</v>
+      </c>
+      <c r="E3" t="str">
+        <v>3</v>
+      </c>
+      <c r="F3" t="str">
+        <v>30</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mise en forme pièces justificatives</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Maintenance matériel</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TM3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Entretien tracteur JD8R</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-06-04 08:00</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-04 12:00</v>
+      </c>
+      <c r="E4" t="str">
+        <v>4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Révision 500h + vidange</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Maintenance matériel</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TM4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Réunion CA mensuelle</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-06-05 18:30</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-05 20:30</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>CA ordinaire – points divers</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Gestion administrative CUMA</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TM5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Formation logiciel planning</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-05-29 09:00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-29 12:00</v>
+      </c>
+      <c r="E6" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Formation adhérents outil réservation en ligne</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Digitalisation adhérents</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TM6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Réparation circuit hydraulique</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-06-06 08:00</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-06 16:00</v>
+      </c>
+      <c r="E7" t="str">
+        <v>8</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Intervention prestataire + supervision CUMA</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Maintenance matériel</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TM7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rédaction newsletter juin</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-06-07 14:00</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-07 16:00</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Rédaction + envoi newsletter adhérents</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Digitalisation adhérents</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="E1" t="str">
+        <v>priorite</v>
+      </c>
+      <c r="F1" t="str">
+        <v>solution</v>
+      </c>
+      <c r="G1" t="str">
+        <v>suivi</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ASS1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Coopérative du Grand-Est</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CGE</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Partenaire actif</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Échanges matériel, formation</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Suivi régulier</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ASS2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Agro-Parts SARL</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AGP</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Fournisseur actif</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fourniture pièces détachées</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Sur demande</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ASS3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Banque Agricole du Rhin</v>
+      </c>
+      <c r="C4" t="str">
+        <v>BAR</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Partenaire financier</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Financement équipements, crédit-bail</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Trimestriel</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ASS4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CA68</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Institution partenaire</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Conseil technique, formation</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Annuel</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ticketId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>sujet</v>
+      </c>
+      <c r="D1" t="str">
+        <v>codeAssoc</v>
+      </c>
+      <c r="E1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="F1" t="str">
+        <v>priorite</v>
+      </c>
+      <c r="G1" t="str">
+        <v>niveau</v>
+      </c>
+      <c r="H1" t="str">
+        <v>dateModif</v>
+      </c>
+      <c r="I1" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="J1" t="str">
+        <v>lien</v>
+      </c>
+      <c r="K1" t="str">
+        <v>zone</v>
+      </c>
+      <c r="L1" t="str">
+        <v>memo</v>
+      </c>
+      <c r="M1" t="str">
+        <v>codeDossier</v>
+      </c>
+      <c r="N1" t="str">
+        <v>categorie</v>
+      </c>
+      <c r="O1" t="str">
+        <v>sousCategorie</v>
+      </c>
+      <c r="P1" t="str">
+        <v>conclusion</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>departement</v>
+      </c>
+      <c r="R1" t="str">
+        <v>associationId</v>
+      </c>
+      <c r="S1" t="str">
+        <v>associationName</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TK1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TK-001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Panne circuit hydraulique JD8R</v>
+      </c>
+      <c r="D2" t="str">
+        <v>CGE</v>
+      </c>
+      <c r="E2" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Majeur</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Pierre Muller</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>Matériel</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Tracteur JD8R immobilisé depuis le 01/06. Intervenant Agro-Parts contacté.</v>
+      </c>
+      <c r="M2" t="str">
+        <v>MAT-2026-031</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Panne</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Hydraulique</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="R2" t="str">
+        <v>ASS1</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Coopérative du Grand-Est</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TK2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TK-002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dysfonctionnement module export Télago</v>
+      </c>
+      <c r="D3" t="str">
+        <v>AGP</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Ouvert</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mineur</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Jean-Claude Weber</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>Logiciel</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Export CSV défaillant depuis mise à jour v4.2.</v>
+      </c>
+      <c r="M3" t="str">
+        <v>LOG-2026-018</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Logiciel</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Export/Import</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>SI</v>
+      </c>
+      <c r="R3" t="str">
+        <v>ASS2</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Agro-Parts SARL</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TK3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TK-003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Erreur facturation adhérent GAEC Schmitt</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BAR</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Résolu</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Mineur</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Mathieu Rapp</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>Administratif</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Double facturation corrigée, avoir émis.</v>
+      </c>
+      <c r="M4" t="str">
+        <v>ADM-2026-012</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Facturation</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Correction</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Avoir de 320 € émis le 22/05</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Comptabilité</v>
+      </c>
+      <c r="R4" t="str">
+        <v>ASS3</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Banque Agricole du Rhin</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TK4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>TK-004</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Conflit réservation tracteur semaine 24</v>
+      </c>
+      <c r="D5" t="str">
+        <v>CGE</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Ouvert</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Majeur</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="I5" t="str">
+        <v>René Ott</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Planning</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2 adhérents ont réservé le même matériel sur les mêmes créneaux.</v>
+      </c>
+      <c r="M5" t="str">
+        <v>PLA-2026-045</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Planning</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Conflit réservation</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>Coordination</v>
+      </c>
+      <c r="R5" t="str">
+        <v>ASS1</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Coopérative du Grand-Est</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TK5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>TK-005</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Demande attestation cotisation sociale annuelle</v>
+      </c>
+      <c r="D6" t="str">
+        <v>CA68</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Qualifié</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Basse</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Mineur</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Nathalie Braun</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>Administratif</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Attestation à générer depuis l'outil Carsat.</v>
+      </c>
+      <c r="M6" t="str">
+        <v>ADM-2026-009</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Attestation</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Social</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>RH</v>
+      </c>
+      <c r="R6" t="str">
+        <v>ASS4</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TK6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TK-006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Double saisie coordonnées GPS parcelles</v>
+      </c>
+      <c r="D7" t="str">
+        <v>AGP</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Suspendu</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Basse</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Mineur</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Christian Fuchs</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>Logiciel</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Problème de synchronisation avec application SigPAC.</v>
+      </c>
+      <c r="M7" t="str">
+        <v>LOG-2026-014</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Données</v>
+      </c>
+      <c r="O7" t="str">
+        <v>GPS/SIG</v>
+      </c>
+      <c r="P7" t="str">
+        <v>En attente mise à jour SigPAC (éditeur)</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>SI</v>
+      </c>
+      <c r="R7" t="str">
+        <v>ASS2</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Agro-Parts SARL</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TK7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TK-007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Déclaration subvention LEADER incorrecte</v>
+      </c>
+      <c r="D8" t="str">
+        <v>BAR</v>
+      </c>
+      <c r="E8" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Majeur</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Isabelle Gasser</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Financier</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Erreur de code NAF sur le formulaire. Recalcul en cours.</v>
+      </c>
+      <c r="M8" t="str">
+        <v>FIN-2026-028</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Subvention</v>
+      </c>
+      <c r="O8" t="str">
+        <v>LEADER</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="R8" t="str">
+        <v>ASS3</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Banque Agricole du Rhin</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TK8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>TK-008</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Organisation session sécurité tracteur CACES R 482</v>
+      </c>
+      <c r="D9" t="str">
+        <v>CA68</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Didier Metz</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>Formation</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Session prévue en octobre 2026. 8 participants identifiés.</v>
+      </c>
+      <c r="M9" t="str">
+        <v>FOR-2026-007</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Formation</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Sécurité CACES</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>RH</v>
+      </c>
+      <c r="R9" t="str">
+        <v>ASS4</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:S9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>titre</v>
+      </c>
+      <c r="C1" t="str">
+        <v>codeTiers</v>
+      </c>
+      <c r="D1" t="str">
+        <v>lieu</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CL1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Métal-Alsace SA</v>
+      </c>
+      <c r="C2" t="str">
+        <v>MA-001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Mulhouse, 68100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CL2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BioGranges Sàrl</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BG-002</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Colmar, 68000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CL3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Holding LVT</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LV-003</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Strasbourg, 67000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>tiers</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tiersId</v>
+      </c>
+      <c r="E1" t="str">
+        <v>typeProjet</v>
+      </c>
+      <c r="F1" t="str">
+        <v>dateDebut</v>
+      </c>
+      <c r="G1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="H1" t="str">
+        <v>statutColor</v>
+      </c>
+      <c r="I1" t="str">
+        <v>codeProjet</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CP1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Audit organisationnel 2026</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Métal-Alsace SA</v>
+      </c>
+      <c r="D2" t="str">
+        <v>CL1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Audit</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="G2" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="H2" t="str">
+        <v>blue</v>
+      </c>
+      <c r="I2" t="str">
+        <v>PJ-1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CP2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Stratégie RSE 2026-2028</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BioGranges Sàrl</v>
+      </c>
+      <c r="D3" t="str">
+        <v>CL2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Stratégie</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="G3" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="H3" t="str">
+        <v>green</v>
+      </c>
+      <c r="I3" t="str">
+        <v>PJ-2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CP3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Plan de fusion LVT</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Holding LVT</v>
+      </c>
+      <c r="D4" t="str">
+        <v>CL3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>M&amp;A</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="G4" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="H4" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I4" t="str">
+        <v>PJ-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L11"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>canal</v>
+      </c>
+      <c r="D1" t="str">
+        <v>canalColor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="F1" t="str">
+        <v>statutColor</v>
+      </c>
+      <c r="G1" t="str">
+        <v>priorite</v>
+      </c>
+      <c r="H1" t="str">
+        <v>prioriteColor</v>
+      </c>
+      <c r="I1" t="str">
+        <v>dateEcheance</v>
+      </c>
+      <c r="J1" t="str">
+        <v>planifieLe</v>
+      </c>
+      <c r="K1" t="str">
+        <v>suivis</v>
+      </c>
+      <c r="L1" t="str">
+        <v>projetId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TAC1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Entretiens dirigeants et COMEX</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D2" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="F2" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H2" t="str">
+        <v>red</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TAC2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Analyse processus RH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Hybride</v>
+      </c>
+      <c r="D3" t="str">
+        <v>purple</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="F3" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H3" t="str">
+        <v>red</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TAC3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Benchmark sectoriel</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="D4" t="str">
+        <v>green</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="F4" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="H4" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TAC4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rapport diagnostic final</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D5" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E5" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F5" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H5" t="str">
+        <v>red</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="J5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TAC5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Diagnostic RSE initial</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="F6" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H6" t="str">
+        <v>red</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="J6" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TAC6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ateliers parties prenantes</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D7" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E7" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F7" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H7" t="str">
+        <v>red</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J7" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TAC7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Feuille de route RSE</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Hybride</v>
+      </c>
+      <c r="D8" t="str">
+        <v>purple</v>
+      </c>
+      <c r="E8" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="F8" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="H8" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TAC8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Due diligence financière</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D9" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E9" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F9" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="H9" t="str">
+        <v>red</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J9" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TAC9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Analyse synergies</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="D10" t="str">
+        <v>green</v>
+      </c>
+      <c r="E10" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="F10" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="H10" t="str">
+        <v>red</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TAC10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Plan d'intégration</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="D11" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E11" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="F11" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="H11" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="D1" t="str">
+        <v>statutColor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>priorite</v>
+      </c>
+      <c r="F1" t="str">
+        <v>prioriteColor</v>
+      </c>
+      <c r="G1" t="str">
+        <v>canal</v>
+      </c>
+      <c r="H1" t="str">
+        <v>canalColor</v>
+      </c>
+      <c r="I1" t="str">
+        <v>date</v>
+      </c>
+      <c r="J1" t="str">
+        <v>tacheNoms</v>
+      </c>
+      <c r="K1" t="str">
+        <v>projetId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ST1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Préparation grille entretiens</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="D2" t="str">
+        <v>gray</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="F2" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="H2" t="str">
+        <v>green</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Entretiens dirigeants et COMEX</v>
+      </c>
+      <c r="K2" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ST2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Transcription et analyse entretiens</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="D3" t="str">
+        <v>gray</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Normale</v>
+      </c>
+      <c r="F3" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="H3" t="str">
+        <v>green</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Entretiens dirigeants et COMEX</v>
+      </c>
+      <c r="K3" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ST3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Questionnaire RSE parties prenantes</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="D4" t="str">
+        <v>gray</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="F4" t="str">
+        <v>red</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="H4" t="str">
+        <v>green</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Ateliers parties prenantes</v>
+      </c>
+      <c r="K4" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ST4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Animation atelier fournisseurs</v>
+      </c>
+      <c r="C5" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="D5" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="F5" t="str">
+        <v>red</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="H5" t="str">
+        <v>blue</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Ateliers parties prenantes</v>
+      </c>
+      <c r="K5" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ST5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Analyse comptable filiales</v>
+      </c>
+      <c r="C6" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="D6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F6" t="str">
+        <v>red</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="H6" t="str">
+        <v>green</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Due diligence financière</v>
+      </c>
+      <c r="K6" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ST6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Revue contrats fournisseurs</v>
+      </c>
+      <c r="C7" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="D7" t="str">
+        <v>orange</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="F7" t="str">
+        <v>red</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="H7" t="str">
+        <v>green</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Due diligence financière</v>
+      </c>
+      <c r="K7" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="E1" t="str">
+        <v>statutColor</v>
+      </c>
+      <c r="F1" t="str">
+        <v>tacheNoms</v>
+      </c>
+      <c r="G1" t="str">
+        <v>projetId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SPJ1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Kick-off mission Métal-Alsace</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="E2" t="str">
+        <v>gray</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SPJ2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Point intermédiaire diagnostic</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="E3" t="str">
+        <v>gray</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Analyse processus RH|Benchmark sectoriel</v>
+      </c>
+      <c r="G3" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SPJ3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Lancement mission RSE BioGranges</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="E4" t="str">
+        <v>gray</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SPJ4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Réunion lancement due diligence</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Terminé</v>
+      </c>
+      <c r="E5" t="str">
+        <v>gray</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SPJ5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Revue avancement due diligence</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="D6" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="E6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Due diligence financière|Analyse synergies</v>
+      </c>
+      <c r="G6" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>canal</v>
+      </c>
+      <c r="E1" t="str">
+        <v>canalColor</v>
+      </c>
+      <c r="F1" t="str">
+        <v>contact</v>
+      </c>
+      <c r="G1" t="str">
+        <v>suivi</v>
+      </c>
+      <c r="H1" t="str">
+        <v>tacheNoms</v>
+      </c>
+      <c r="I1" t="str">
+        <v>projetId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>EX1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Réunion cadrage mission</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="E2" t="str">
+        <v>blue</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Directeur RH|DG</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Kick-off mission Métal-Alsace</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>EX2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Email compte-rendu entretiens</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Email</v>
+      </c>
+      <c r="E3" t="str">
+        <v>gray</v>
+      </c>
+      <c r="F3" t="str">
+        <v>DRH</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Entretiens dirigeants et COMEX</v>
+      </c>
+      <c r="I3" t="str">
+        <v>CP1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>EX3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Réunion comité RSE BioGranges</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="E4" t="str">
+        <v>blue</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CEO BioGranges|RSE Manager</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Diagnostic RSE initial</v>
+      </c>
+      <c r="I4" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>EX4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Appel suivi ateliers RSE</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Téléphone</v>
+      </c>
+      <c r="E5" t="str">
+        <v>green</v>
+      </c>
+      <c r="F5" t="str">
+        <v>RSE Manager</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>Ateliers parties prenantes</v>
+      </c>
+      <c r="I5" t="str">
+        <v>CP2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>EX5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Réunion kick-off plan fusion</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Présentiel</v>
+      </c>
+      <c r="E6" t="str">
+        <v>blue</v>
+      </c>
+      <c r="F6" t="str">
+        <v>CFO LVT|DAF LVT</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Réunion lancement due diligence</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>EX6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Revue due diligence en visio</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Visioconférence</v>
+      </c>
+      <c r="E7" t="str">
+        <v>purple</v>
+      </c>
+      <c r="F7" t="str">
+        <v>CFO LVT</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Revue avancement due diligence</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Due diligence financière</v>
+      </c>
+      <c r="I7" t="str">
+        <v>CP3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>statut</v>
+      </c>
+      <c r="D1" t="str">
+        <v>statutColor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>projet</v>
+      </c>
+      <c r="G1" t="str">
+        <v>projetId</v>
+      </c>
+      <c r="H1" t="str">
+        <v>blocks_json</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DOC1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rapport diagnostic préliminaire</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Brouillon</v>
+      </c>
+      <c r="D2" t="str">
+        <v>orange</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Audit organisationnel 2026</v>
+      </c>
+      <c r="G2" t="str">
+        <v>CP1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Synthèse exécutive","href":null,"text":{"content":"Synthèse exécutive"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Audit de 6 semaines réalisé de février à mars 2026. 14 entretiens conduits auprès des membres du COMEX et des managers clés.","href":null,"text":{"content":"Audit de 6 semaines réalisé de février à mars 2026. 14 entretiens conduits auprès des membres du COMEX et des managers clés."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Constats principaux","href":null,"text":{"content":"Constats principaux"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Structure organisationnelle morcelée : 7 niveaux hiérarchiques vs 4 dans le secteur","href":null,"text":{"content":"Structure organisationnelle morcelée : 7 niveaux hiérarchiques vs 4 dans le secteur"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Processus RH non standardisés entre les 3 sites de production","href":null,"text":{"content":"Processus RH non standardisés entre les 3 sites de production"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Potentiel d'économies estimé à 8-12 % de la masse salariale sur 3 ans","href":null,"text":{"content":"Potentiel d'économies estimé à 8-12 % de la masse salariale sur 3 ans"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Turn-over élevé dans les équipes opérationnelles : 18 % vs 11 % secteur","href":null,"text":{"content":"Turn-over élevé dans les équipes opérationnelles : 18 % vs 11 % secteur"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Recommandations prioritaires","href":null,"text":{"content":"Recommandations prioritaires"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Aplatir la structure : passer de 7 à 4 niveaux hiérarchiques","href":null,"text":{"content":"Aplatir la structure : passer de 7 à 4 niveaux hiérarchiques"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Déployer un SIRH unifié pour les 3 sites","href":null,"text":{"content":"Déployer un SIRH unifié pour les 3 sites"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Mettre en place un programme de fidélisation des talents","href":null,"text":{"content":"Mettre en place un programme de fidélisation des talents"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk012","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Prochaines étapes","href":null,"text":{"content":"Prochaines étapes"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk013","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Présentation au COMEX prévue le 25 juin 2026. Validation plan d'action attendue avant fin juillet.","href":null,"text":{"content":"Présentation au COMEX prévue le 25 juin 2026. Validation plan d'action attendue avant fin juillet."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DOC2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Note de cadrage mission</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D3" t="str">
+        <v>green</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Audit organisationnel 2026</v>
+      </c>
+      <c r="G3" t="str">
+        <v>CP1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Périmètre de la mission","href":null,"text":{"content":"Périmètre de la mission"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Mission d'audit organisationnel portant sur les fonctions RH, Finance et Opérations de Métal-Alsace SA (3 sites, 320 collaborateurs).","href":null,"text":{"content":"Mission d'audit organisationnel portant sur les fonctions RH, Finance et Opérations de Métal-Alsace SA (3 sites, 320 collaborateurs)."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Équipe projet","href":null,"text":{"content":"Équipe projet"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"CAP Consulting : 2 consultants senior + 1 analyste","href":null,"text":{"content":"CAP Consulting : 2 consultants senior + 1 analyste"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Métal-Alsace : DRH, DAF, COO","href":null,"text":{"content":"Métal-Alsace : DRH, DAF, COO"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Planning","href":null,"text":{"content":"Planning"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Phase 1 – Diagnostic (6 semaines) : fév.-mars 2026","href":null,"text":{"content":"Phase 1 – Diagnostic (6 semaines) : fév.-mars 2026"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Phase 2 – Recommandations (3 semaines) : avr. 2026","href":null,"text":{"content":"Phase 2 – Recommandations (3 semaines) : avr. 2026"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Phase 3 – Plan d'action (2 semaines) : mai 2026","href":null,"text":{"content":"Phase 3 – Plan d'action (2 semaines) : mai 2026"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Budget","href":null,"text":{"content":"Budget"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Honoraires fixés à 45 000 € HT selon proposition commerciale PC-2025-047.","href":null,"text":{"content":"Honoraires fixés à 45 000 € HT selon proposition commerciale PC-2025-047."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DOC3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Présentation CODIR RSE</v>
+      </c>
+      <c r="C4" t="str">
+        <v>En révision</v>
+      </c>
+      <c r="D4" t="str">
+        <v>orange</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Stratégie RSE 2026-2028</v>
+      </c>
+      <c r="G4" t="str">
+        <v>CP2</v>
+      </c>
+      <c r="H4" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Objet de la présentation","href":null,"text":{"content":"Objet de la présentation"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Présentation du projet de Stratégie RSE 2026-2028 au Comité de Direction de BioGranges Sàrl.","href":null,"text":{"content":"Présentation du projet de Stratégie RSE 2026-2028 au Comité de Direction de BioGranges Sàrl."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Messages clés","href":null,"text":{"content":"Messages clés"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"BioGranges peut viser une certification Ecocert niveau 3 d'ici 2027","href":null,"text":{"content":"BioGranges peut viser une certification Ecocert niveau 3 d'ici 2027"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"3 axes prioritaires : énergie renouvelable, traçabilité amont, emploi local","href":null,"text":{"content":"3 axes prioritaires : énergie renouvelable, traçabilité amont, emploi local"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"ROI estimé sur 3 ans : économies 120 000 € + attractivité marque +15 %","href":null,"text":{"content":"ROI estimé sur 3 ans : économies 120 000 € + attractivité marque +15 %"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Questions ouvertes","href":null,"text":{"content":"Questions ouvertes"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Validation du budget RSE (85 000 € prévu vs 60 000 € demandé). Arbitrage attendu au prochain CA.","href":null,"text":{"content":"Validation du budget RSE (85 000 € prévu vs 60 000 € demandé). Arbitrage attendu au prochain CA."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Décisions attendues","href":null,"text":{"content":"Décisions attendues"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Validation du périmètre des 3 axes","href":null,"text":{"content":"Validation du périmètre des 3 axes"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Nomination du responsable RSE interne","href":null,"text":{"content":"Nomination du responsable RSE interne"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk012","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Calendrier de communication externe","href":null,"text":{"content":"Calendrier de communication externe"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DOC4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rapport due diligence</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Brouillon</v>
+      </c>
+      <c r="D5" t="str">
+        <v>orange</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Plan de fusion LVT</v>
+      </c>
+      <c r="G5" t="str">
+        <v>CP3</v>
+      </c>
+      <c r="H5" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Périmètre","href":null,"text":{"content":"Périmètre"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Due diligence financière et juridique portant sur les 4 filiales du périmètre de fusion : LVT Industrie, LVT Services, LVT Immobilier, LVT Digital.","href":null,"text":{"content":"Due diligence financière et juridique portant sur les 4 filiales du périmètre de fusion : LVT Industrie, LVT Services, LVT Immobilier, LVT Digital."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Principaux enseignements","href":null,"text":{"content":"Principaux enseignements"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Bilan consolidé sain : ratio d'endettement 1,4× EBITDA","href":null,"text":{"content":"Bilan consolidé sain : ratio d'endettement 1,4× EBITDA"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Risque contentieux identifié : litige fournisseur (200 000 € provisionnés)","href":null,"text":{"content":"Risque contentieux identifié : litige fournisseur (200 000 € provisionnés)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"LVT Digital : valorisation à revoir (goodwill surestimé de 15 %)","href":null,"text":{"content":"LVT Digital : valorisation à revoir (goodwill surestimé de 15 %)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Axes de vigilance","href":null,"text":{"content":"Axes de vigilance"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Transferts intra-groupe à documenter pour la holding réorganisée","href":null,"text":{"content":"Transferts intra-groupe à documenter pour la holding réorganisée"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Pacte d'actionnaires à harmoniser entre les filiales","href":null,"text":{"content":"Pacte d'actionnaires à harmoniser entre les filiales"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Suite recommandée","href":null,"text":{"content":"Suite recommandée"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Engagement d'un cabinet juridique spécialisé M&amp;A pour sécuriser le montage. Budget estimé : 25 000 €.","href":null,"text":{"content":"Engagement d'un cabinet juridique spécialisé M&amp;A pour sécuriser le montage. Budget estimé : 25 000 €."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DOC5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Plan d'intégration LVT Group</v>
+      </c>
+      <c r="C6" t="str">
+        <v>À rédiger</v>
+      </c>
+      <c r="D6" t="str">
+        <v>gray</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Plan de fusion LVT</v>
+      </c>
+      <c r="G6" t="str">
+        <v>CP3</v>
+      </c>
+      <c r="H6" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Objectifs du plan","href":null,"text":{"content":"Objectifs du plan"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Feuille de route pour l'intégration opérationnelle des 4 filiales sous la nouvelle holding LVT Group, d'ici T1 2027.","href":null,"text":{"content":"Feuille de route pour l'intégration opérationnelle des 4 filiales sous la nouvelle holding LVT Group, d'ici T1 2027."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Chantiers prioritaires","href":null,"text":{"content":"Chantiers prioritaires"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Chantier 1 – Gouvernance : recomposition du CA consolidé (sept. 2026)","href":null,"text":{"content":"Chantier 1 – Gouvernance : recomposition du CA consolidé (sept. 2026)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Chantier 2 – Finance : unification du reporting (oct. 2026)","href":null,"text":{"content":"Chantier 2 – Finance : unification du reporting (oct. 2026)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Chantier 3 – RH : harmonisation statuts et avantages (déc. 2026)","href":null,"text":{"content":"Chantier 3 – RH : harmonisation statuts et avantages (déc. 2026)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Chantier 4 – SI : cartographie des systèmes et plan de convergence (T1 2027)","href":null,"text":{"content":"Chantier 4 – SI : cartographie des systèmes et plan de convergence (T1 2027)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Indicateurs de succès","href":null,"text":{"content":"Indicateurs de succès"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Synergies réalisées : objectif 1,2 M€ sur 3 ans","href":null,"text":{"content":"Synergies réalisées : objectif 1,2 M€ sur 3 ans"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Rétention talents clés : &gt; 90 % à 12 mois","href":null,"text":{"content":"Rétention talents clés : &gt; 90 % à 12 mois"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Délai intégration : 18 mois maximum","href":null,"text":{"content":"Délai intégration : 18 mois maximum"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
@@ -520,702 +2856,1453 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:J9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>project_id</v>
+        <v>description</v>
       </c>
       <c r="C1" t="str">
-        <v>title</v>
+        <v>debut</v>
       </c>
       <c r="D1" t="str">
-        <v>start_date</v>
+        <v>fin</v>
       </c>
       <c r="E1" t="str">
-        <v>end_date</v>
+        <v>dureeH</v>
       </c>
       <c r="F1" t="str">
-        <v>assignee_id</v>
+        <v>dureeMin</v>
       </c>
       <c r="G1" t="str">
-        <v>status</v>
+        <v>tacheNoms</v>
       </c>
       <c r="H1" t="str">
-        <v>planned</v>
+        <v>facturable</v>
+      </c>
+      <c r="I1" t="str">
+        <v>facturableH</v>
+      </c>
+      <c r="J1" t="str">
+        <v>projetId</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>T01</v>
+        <v>TP1</v>
       </c>
       <c r="B2" t="str">
-        <v>P1</v>
+        <v>Entretiens dirigeants (J1)</v>
       </c>
       <c r="C2" t="str">
-        <v>Audit UX site actuel</v>
+        <v>2026-02-20 09:00</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-20 17:00</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-01</v>
+        <v>8</v>
       </c>
       <c r="F2" t="str">
-        <v>U1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>done</v>
+        <v>Entretiens dirigeants et COMEX</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2" t="str">
+        <v>8</v>
+      </c>
+      <c r="J2" t="str">
+        <v>CP1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>T02</v>
+        <v>TP2</v>
       </c>
       <c r="B3" t="str">
-        <v>P1</v>
+        <v>Analyse processus RH (J1)</v>
       </c>
       <c r="C3" t="str">
-        <v>Wireframes nouvelle home</v>
+        <v>2026-03-05 09:00</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-02</v>
+        <v>2026-03-05 17:30</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-09</v>
+        <v>8</v>
       </c>
       <c r="F3" t="str">
-        <v>U1</v>
+        <v>30</v>
       </c>
       <c r="G3" t="str">
-        <v>in_progress</v>
+        <v>Analyse processus RH</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="J3" t="str">
+        <v>CP1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>T03</v>
+        <v>TP3</v>
       </c>
       <c r="B4" t="str">
-        <v>P1</v>
+        <v>Diagnostic RSE terrain (J1)</v>
       </c>
       <c r="C4" t="str">
-        <v>Maquettes Figma pages clés</v>
+        <v>2026-04-08 09:00</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-07</v>
+        <v>2026-04-08 18:00</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-19</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>U2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>in_progress</v>
+        <v>Diagnostic RSE initial</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4" t="str">
+        <v>9</v>
+      </c>
+      <c r="J4" t="str">
+        <v>CP2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>T04</v>
+        <v>TP4</v>
       </c>
       <c r="B5" t="str">
-        <v>P1</v>
+        <v>Atelier parties prenantes</v>
       </c>
       <c r="C5" t="str">
-        <v>Validation client maquettes</v>
+        <v>2026-06-12 09:00</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-20</v>
+        <v>2026-06-12 17:00</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-22</v>
+        <v>8</v>
       </c>
       <c r="F5" t="str">
-        <v>U1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>todo</v>
+        <v>Ateliers parties prenantes</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
+      <c r="I5" t="str">
+        <v>8</v>
+      </c>
+      <c r="J5" t="str">
+        <v>CP2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>T05</v>
+        <v>TP5</v>
       </c>
       <c r="B6" t="str">
-        <v>P1</v>
+        <v>Préparation feuille de route RSE</v>
       </c>
       <c r="C6" t="str">
-        <v>Intégration HTML/CSS</v>
+        <v>2026-06-15 14:00</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-23</v>
+        <v>2026-06-15 18:00</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-22</v>
+        <v>4</v>
       </c>
       <c r="F6" t="str">
-        <v>U2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>todo</v>
+        <v>Feuille de route RSE</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <v>CP2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>T06</v>
+        <v>TP6</v>
       </c>
       <c r="B7" t="str">
-        <v>P1</v>
+        <v>Réunion kick-off fusion LVT</v>
       </c>
       <c r="C7" t="str">
-        <v>Migration contenu</v>
+        <v>2026-05-06 09:00</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-07-12</v>
+        <v>2026-05-06 12:00</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-27</v>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
-        <v>U3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>todo</v>
+        <v/>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
+      <c r="I7" t="str">
+        <v>3</v>
+      </c>
+      <c r="J7" t="str">
+        <v>CP3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>T07</v>
+        <v>TP7</v>
       </c>
       <c r="B8" t="str">
-        <v>P1</v>
+        <v>Revue due diligence financière</v>
       </c>
       <c r="C8" t="str">
-        <v>Mise en ligne + redirections</v>
+        <v>2026-06-06 09:00</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-07-28</v>
+        <v>2026-06-06 17:00</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-04</v>
+        <v>8</v>
       </c>
       <c r="F8" t="str">
-        <v>U2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>todo</v>
+        <v>Due diligence financière</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
+      <c r="I8" t="str">
+        <v>8</v>
+      </c>
+      <c r="J8" t="str">
+        <v>CP3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>T08</v>
+        <v>TP8</v>
       </c>
       <c r="B9" t="str">
-        <v>P2</v>
+        <v>Analyse synergies (amorçage)</v>
       </c>
       <c r="C9" t="str">
-        <v>Cadrage offre commerciale</v>
+        <v>2026-06-08 14:00</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-08 17:00</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-17</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>U1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>todo</v>
+        <v>Analyse synergies</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>T09</v>
-      </c>
-      <c r="B10" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Dev backend API produit</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-06-18</v>
-      </c>
-      <c r="E10" t="str">
-        <v>2026-08-06</v>
-      </c>
-      <c r="F10" t="str">
-        <v>U2</v>
-      </c>
-      <c r="G10" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>T10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Création visuels marketing</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-06-27</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-07-17</v>
-      </c>
-      <c r="F11" t="str">
-        <v>U3</v>
-      </c>
-      <c r="G11" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>T11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Beta test utilisateurs</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-08-11</v>
-      </c>
-      <c r="E12" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="F12" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G12" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>T12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Lancement officiel</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-09-05</v>
-      </c>
-      <c r="E13" t="str">
-        <v>2026-09-07</v>
-      </c>
-      <c r="F13" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G13" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>T13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Cartographie données existantes</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-06-12</v>
-      </c>
-      <c r="E14" t="str">
-        <v>2026-07-02</v>
-      </c>
-      <c r="F14" t="str">
-        <v>U3</v>
-      </c>
-      <c r="G14" t="str">
-        <v>in_progress</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>T14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Spec techniques migration</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-07-03</v>
-      </c>
-      <c r="E15" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="F15" t="str">
-        <v>U2</v>
-      </c>
-      <c r="G15" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>T15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Dev scripts ETL</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-07-23</v>
-      </c>
-      <c r="E16" t="str">
-        <v>2026-09-15</v>
-      </c>
-      <c r="F16" t="str">
-        <v>U2</v>
-      </c>
-      <c r="G16" t="str">
-        <v>blocked</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>T16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Recette comptable</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-09-16</v>
-      </c>
-      <c r="E17" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="F17" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G17" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>T17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Bascule production</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-10-15</v>
-      </c>
-      <c r="E18" t="str">
-        <v>2026-10-20</v>
-      </c>
-      <c r="F18" t="str">
-        <v>U3</v>
-      </c>
-      <c r="G18" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>T18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Formation utilisateurs finaux</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-10-25</v>
-      </c>
-      <c r="E19" t="str">
-        <v>2026-11-09</v>
-      </c>
-      <c r="F19" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G19" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>U01</v>
-      </c>
-      <c r="B20" t="str">
-        <v>P1</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Optimisation SEO technique</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v>U2</v>
-      </c>
-      <c r="G20" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>U02</v>
-      </c>
-      <c r="B21" t="str">
-        <v>P1</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Refonte page tarifs</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G21" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>U03</v>
-      </c>
-      <c r="B22" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Étude marché concurrent</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G22" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>U04</v>
-      </c>
-      <c r="B23" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Plan de communication presse</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>U3</v>
-      </c>
-      <c r="G23" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>U05</v>
-      </c>
-      <c r="B24" t="str">
-        <v>P2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Préparation pitch investisseurs</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v>U1</v>
-      </c>
-      <c r="G24" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>U06</v>
-      </c>
-      <c r="B25" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Documentation utilisateur</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v>U2</v>
-      </c>
-      <c r="G25" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>U07</v>
-      </c>
-      <c r="B26" t="str">
-        <v>P3</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Plan de reprise après incident</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v>U3</v>
-      </c>
-      <c r="G26" t="str">
-        <v>todo</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
+      <c r="I9" t="str">
+        <v>3</v>
+      </c>
+      <c r="J9" t="str">
+        <v>CP3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>project_id</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SP1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Phase 1 – Analyse &amp; maquettes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>P1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SP2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Phase 2 – Développement</v>
+      </c>
+      <c r="C3" t="str">
+        <v>P1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SP3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Phase 1 – Backend API</v>
+      </c>
+      <c r="C4" t="str">
+        <v>P2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:I37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
+        <v>project_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>subproject_id</v>
+      </c>
+      <c r="D1" t="str">
+        <v>title</v>
+      </c>
+      <c r="E1" t="str">
+        <v>start_date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>end_date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>assignee_id</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>planned</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>T01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>Audit UX site actuel</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="G2" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>done</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>T02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SP1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Wireframes nouvelle home</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-06-13</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-06-20</v>
+      </c>
+      <c r="G3" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>in_progress</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>T03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SP1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Maquettes Figma pages clés</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="G4" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H4" t="str">
+        <v>in_progress</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>T04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>Validation client maquettes</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="G5" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H5" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>T05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SP2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Intégration HTML/CSS</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-07-04</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-08-02</v>
+      </c>
+      <c r="G6" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H6" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>T06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SP2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Migration contenu</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-07-23</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-08-07</v>
+      </c>
+      <c r="G7" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H7" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>T07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SP2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Mise en ligne + redirections</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-08-08</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="G8" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H8" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>T08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>Optimisation performances</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-06</v>
+      </c>
+      <c r="G9" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H9" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>T09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Campagne SEO post-lancement</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="G10" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H10" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>T10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Bilan 3 mois post-lancement</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-10-11</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="G11" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>T11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Préparation budget 2027</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-11-15</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-12-05</v>
+      </c>
+      <c r="G12" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H12" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>T12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Cadrage offre commerciale</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="G13" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>T13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>SP3</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Dev backend API produit</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="G14" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H14" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>T14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Création visuels marketing</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="G15" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H15" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>T15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>Recrutement développeur senior</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="G16" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H16" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>T16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Beta test utilisateurs</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="G17" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H17" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>T17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Lancement officiel</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="G18" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H18" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>T18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Onboarding premiers clients</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="G19" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H19" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>T19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>Correctifs v1.1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-10-11</v>
+      </c>
+      <c r="G20" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H20" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>T20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>Roadmap v2.0</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-11-20</v>
+      </c>
+      <c r="G21" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H21" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>T21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>Cartographie données existantes</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="G22" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H22" t="str">
+        <v>in_progress</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>T22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Spec techniques migration</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-08-02</v>
+      </c>
+      <c r="G23" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H23" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>T23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Dev scripts ETL</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="G24" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H24" t="str">
+        <v>blocked</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>T24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Recette comptable</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="G25" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H25" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>T25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Bascule production</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="G26" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H26" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>T26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Formation utilisateurs finaux</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-11-05</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-11-20</v>
+      </c>
+      <c r="G27" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H27" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>T27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Clôture projet &amp; bilan</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-11-21</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-11-27</v>
+      </c>
+      <c r="G28" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H28" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>T28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Audit post-migration</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-12-30</v>
+      </c>
+      <c r="G29" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H29" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>T29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Documentation maintenance</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-12-20</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2027-01-09</v>
+      </c>
+      <c r="G30" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H30" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>U01</v>
+      </c>
+      <c r="B31" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Optimisation SEO technique</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H31" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>U02</v>
+      </c>
+      <c r="B32" t="str">
+        <v>P1</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Refonte page tarifs</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H32" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>U03</v>
+      </c>
+      <c r="B33" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Étude marché concurrent</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H33" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>U04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>Plan de communication presse</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H34" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>U05</v>
+      </c>
+      <c r="B35" t="str">
+        <v>P2</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>Préparation pitch investisseurs</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>U1</v>
+      </c>
+      <c r="H35" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>U06</v>
+      </c>
+      <c r="B36" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>Documentation utilisateur</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>U2</v>
+      </c>
+      <c r="H36" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>U07</v>
+      </c>
+      <c r="B37" t="str">
+        <v>P3</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>Plan de reprise après incident</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>U3</v>
+      </c>
+      <c r="H37" t="str">
+        <v>todo</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I37"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
         <v>title</v>
       </c>
       <c r="C1" t="str">
@@ -1236,10 +4323,10 @@
         <v>Daily équipe</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-05-29 09:30</v>
+        <v>2026-06-09 09:30</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-29 10:00</v>
+        <v>2026-06-09 10:00</v>
       </c>
       <c r="E2" t="str">
         <v>U1,U2</v>
@@ -1253,10 +4340,10 @@
         <v>RDV client Refonte</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-05-31 14:00</v>
+        <v>2026-06-11 14:00</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-31 15:30</v>
+        <v>2026-06-11 15:30</v>
       </c>
       <c r="E3" t="str">
         <v>U1,U3</v>
@@ -1270,10 +4357,10 @@
         <v>Démo sprint</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-06-04 16:00</v>
+        <v>2026-06-15 16:00</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-04 17:00</v>
+        <v>2026-06-15 17:00</v>
       </c>
       <c r="E4" t="str">
         <v>U1,U2,U3</v>
@@ -1287,10 +4374,10 @@
         <v>Comité de pilotage</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-06-11 10:00</v>
+        <v>2026-06-22 10:00</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-11 12:00</v>
+        <v>2026-06-22 12:00</v>
       </c>
       <c r="E5" t="str">
         <v>U1</v>
@@ -1304,10 +4391,10 @@
         <v>Atelier UX produit X</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-06-15 09:00</v>
+        <v>2026-06-26 09:00</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-15 12:00</v>
+        <v>2026-06-26 12:00</v>
       </c>
       <c r="E6" t="str">
         <v>U1,U2</v>
@@ -1321,10 +4408,10 @@
         <v>Déjeuner partenaire</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-06-19 12:30</v>
+        <v>2026-06-30 12:30</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-19 14:00</v>
+        <v>2026-06-30 14:00</v>
       </c>
       <c r="E7" t="str">
         <v>U1</v>
@@ -1338,10 +4425,10 @@
         <v>Rétro mensuelle</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-06-27 15:00</v>
+        <v>2026-07-08 15:00</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-27 17:00</v>
+        <v>2026-07-08 17:00</v>
       </c>
       <c r="E8" t="str">
         <v>U1,U2,U3</v>
@@ -1355,10 +4442,10 @@
         <v>Formation Notion équipe</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-07-09 14:00</v>
+        <v>2026-07-20 14:00</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-07-09 16:00</v>
+        <v>2026-07-20 16:00</v>
       </c>
       <c r="E9" t="str">
         <v>U2,U3</v>
@@ -1372,10 +4459,10 @@
         <v>Revue budget Q3</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-07-22 10:00</v>
+        <v>2026-08-02 10:00</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-07-22 11:30</v>
+        <v>2026-08-02 11:30</v>
       </c>
       <c r="E10" t="str">
         <v>U1</v>
@@ -1389,10 +4476,10 @@
         <v>Workshop migration ERP</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-08-01 09:00</v>
+        <v>2026-08-12 09:00</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-08-01 17:00</v>
+        <v>2026-08-12 17:00</v>
       </c>
       <c r="E11" t="str">
         <v>U1,U2,U3</v>
@@ -1406,10 +4493,10 @@
         <v>Conférence sectorielle</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-08-24 09:00</v>
+        <v>2026-09-04 09:00</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-08-24 18:00</v>
+        <v>2026-09-04 18:00</v>
       </c>
       <c r="E12" t="str">
         <v>U1</v>
@@ -1423,18 +4510,565 @@
         <v>Bilan annuel client</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-09-25 14:00</v>
+        <v>2026-10-06 14:00</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-09-25 16:00</v>
+        <v>2026-10-06 16:00</v>
       </c>
       <c r="E13" t="str">
         <v>U1,U3</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>G13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sprint review Q3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-09-11 14:00</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-09-11 16:00</v>
+      </c>
+      <c r="E14" t="str">
+        <v>U1,U2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>G14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Séminaire équipe</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-10-26 09:00</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-10-26 18:00</v>
+      </c>
+      <c r="E15" t="str">
+        <v>U1,U2,U3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E1" t="str">
+        <v>blocks_json</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BR1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AG ordinaire – bilan exercice 2025</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Approbation des comptes, vote plan investissement matériel 2026</v>
+      </c>
+      <c r="E2" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Points abordés","href":null,"text":{"content":"Points abordés"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Présentation des comptes 2025 : excédent de 12 400 €","href":null,"text":{"content":"Présentation des comptes 2025 : excédent de 12 400 €"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Rapport du commissaire aux comptes : quitus donné","href":null,"text":{"content":"Rapport du commissaire aux comptes : quitus donné"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Vote plan d'investissement 2026 : tracteur JD8R approuvé (budget 285 000 €)","href":null,"text":{"content":"Vote plan d'investissement 2026 : tracteur JD8R approuvé (budget 285 000 €)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Élection CA : 3 membres renouvelés","href":null,"text":{"content":"Élection CA : 3 membres renouvelés"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Décisions votées","href":null,"text":{"content":"Décisions votées"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Budget investissement 2026 validé. Autorisation accordée au Président de négocier le crédit-bail avec la Banque Agricole du Rhin.","href":null,"text":{"content":"Budget investissement 2026 validé. Autorisation accordée au Président de négocier le crédit-bail avec la Banque Agricole du Rhin."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BR2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Comité de pilotage – renouvellement parc tracteurs</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Validation devis tracteurs John Deere, budget 285 000 €</v>
+      </c>
+      <c r="E3" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Ordre du jour","href":null,"text":{"content":"Ordre du jour"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Validation devis tracteur John Deere 6R 185","href":null,"text":{"content":"Validation devis tracteur John Deere 6R 185"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Arbitrage financement crédit-bail vs achat comptant","href":null,"text":{"content":"Arbitrage financement crédit-bail vs achat comptant"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Planning livraison et mise en service","href":null,"text":{"content":"Planning livraison et mise en service"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Décisions","href":null,"text":{"content":"Décisions"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Devis John Deere validé à 145 000 € HT. Négociation crédit-bail 5 ans confiée à M. Zimmermann. Livraison souhaitée avant les moissons (juillet 2026).","href":null,"text":{"content":"Devis John Deere validé à 145 000 € HT. Négociation crédit-bail 5 ans confiée à M. Zimmermann. Livraison souhaitée avant les moissons (juillet 2026)."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BR3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Point hebdo – digitalisation adhérents</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Avancement appli mobile, connexion API préfecture, démo prévue</v>
+      </c>
+      <c r="E4" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Avancement","href":null,"text":{"content":"Avancement"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Appli mobile : développement en cours (75 % du module réservations). Livraison prévue semaine 30.","href":null,"text":{"content":"Appli mobile : développement en cours (75 % du module réservations). Livraison prévue semaine 30."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Points à traiter","href":null,"text":{"content":"Points à traiter"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"API Préfecture : tests d'intégration en attente d'accès (demande formulée le 20 mai)","href":null,"text":{"content":"API Préfecture : tests d'intégration en attente d'accès (demande formulée le 20 mai)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Démo appli : planifier entre le 15 et 25 juillet pour le CA","href":null,"text":{"content":"Démo appli : planifier entre le 15 et 25 juillet pour le CA"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Mise à jour emails adhérents : campagne de collecte à préparer (objectif 80 %)","href":null,"text":{"content":"Mise à jour emails adhérents : campagne de collecte à préparer (objectif 80 %)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BR4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Réunion budget – plan prévisionnel 2026-2027</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Présentation CA, ajustement cotisations, plan pluriannuel validé en principe</v>
+      </c>
+      <c r="E5" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Synthèse des échanges","href":null,"text":{"content":"Synthèse des échanges"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Présentation du plan prévisionnel 2 ans. Trésorerie solide (réserves 85 000 €). Investissements prévus : tracteur (145 k€) + améliorations bâtiment hangar (22 k€).","href":null,"text":{"content":"Présentation du plan prévisionnel 2 ans. Trésorerie solide (réserves 85 000 €). Investissements prévus : tracteur (145 k€) + améliorations bâtiment hangar (22 k€)."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Points de vigilance","href":null,"text":{"content":"Points de vigilance"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Cotisation 2027 : hausse de 5 % proposée pour absorber le remboursement crédit-bail","href":null,"text":{"content":"Cotisation 2027 : hausse de 5 % proposée pour absorber le remboursement crédit-bail"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Subventions attendues : PCAE ≈ 22 k€, LEADER ≈ 8 k€ (dossier en cours)","href":null,"text":{"content":"Subventions attendues : PCAE ≈ 22 k€, LEADER ≈ 8 k€ (dossier en cours)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Suite","href":null,"text":{"content":"Suite"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Vote final prévu lors de l'AG extraordinaire du 2 septembre 2026.","href":null,"text":{"content":"Vote final prévu lors de l'AG extraordinaire du 2 septembre 2026."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>createdTime</v>
+      </c>
+      <c r="D1" t="str">
+        <v>dueDate</v>
+      </c>
+      <c r="E1" t="str">
+        <v>status</v>
+      </c>
+      <c r="F1" t="str">
+        <v>statusColor</v>
+      </c>
+      <c r="G1" t="str">
+        <v>blocks_json</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PI1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Relancer Agro-Parts pour devis pneumatiques</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-05-20T10:00:00.000Z</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="E2" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="F2" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G2" t="str">
+        <v>[{"id":"bk001","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Devis demandé verbalement le 20 mai. Pas de retour à ce jour.","href":null,"text":{"content":"Devis demandé verbalement le 20 mai. Pas de retour à ce jour."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Contact : M. Faber – 03 89 xx xx xx","href":null,"text":{"content":"Contact : M. Faber – 03 89 xx xx xx"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PI2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Vérifier attestation Urssaf avant AG de juillet</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-06-01T09:00:00.000Z</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="F3" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G3" t="str">
+        <v>[{"id":"bk001","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Attestation annuelle à demander avant le 1er juillet pour l'AG.","href":null,"text":{"content":"Attestation annuelle à demander avant le 1er juillet pour l'AG."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Vérifier sur Net-Entreprises rubrique « Attestations »","href":null,"text":{"content":"Vérifier sur Net-Entreprises rubrique « Attestations »"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Imprimer et joindre au dossier AG","href":null,"text":{"content":"Imprimer et joindre au dossier AG"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PI3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Réserver salle Mairie pour réunion adhérents sept.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-06-04T14:30:00.000Z</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="F4" t="str">
+        <v>gray</v>
+      </c>
+      <c r="G4" t="str">
+        <v>[{"id":"bk001","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Réunion adhérents prévue semaine du 7 septembre 2026.","href":null,"text":{"content":"Réunion adhérents prévue semaine du 7 septembre 2026."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Contacter Secrétariat Mairie de Gundolsheim – Tel : 03 89 yy yy yy","href":null,"text":{"content":"Contacter Secrétariat Mairie de Gundolsheim – Tel : 03 89 yy yy yy"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>shortCode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>etatSuivis</v>
+      </c>
+      <c r="E1" t="str">
+        <v>types</v>
+      </c>
+      <c r="F1" t="str">
+        <v>icon_json</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PA1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Coopérative du Grand-Est</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CGE</v>
+      </c>
+      <c r="D2" t="str">
+        <v>[Ouverts : 2] [En cours : 1]</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Partenaire|Institution</v>
+      </c>
+      <c r="F2" t="str">
+        <v>{"type":"emoji","emoji":"🌾"}</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PA2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Agro-Parts SARL</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AGP</v>
+      </c>
+      <c r="D3" t="str">
+        <v>[Ouverts : 1]</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Fournisseur</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{"type":"emoji","emoji":"⚙️"}</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PA3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CA68</v>
+      </c>
+      <c r="D4" t="str">
+        <v>[En cours : 1] [Clôturés : 1]</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Institution</v>
+      </c>
+      <c r="F4" t="str">
+        <v>{"type":"emoji","emoji":"🏛️"}</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PA4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Banque Agricole du Rhin</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BAR</v>
+      </c>
+      <c r="D5" t="str">
+        <v>[Ouverts : 1] [En cours : 2]</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Partenaire</v>
+      </c>
+      <c r="F5" t="str">
+        <v>{"type":"emoji","emoji":"🏦"}</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>suivi</v>
+      </c>
+      <c r="D1" t="str">
+        <v>suiviColor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>projets</v>
+      </c>
+      <c r="F1" t="str">
+        <v>partenaires</v>
+      </c>
+      <c r="G1" t="str">
+        <v>contact</v>
+      </c>
+      <c r="H1" t="str">
+        <v>createdTime</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lastActionDate</v>
+      </c>
+      <c r="J1" t="str">
+        <v>blocks_json</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SV1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Fourniture pièces hydrauliques JD8R</v>
+      </c>
+      <c r="C2" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="D2" t="str">
+        <v>orange</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Migration ERP</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Agro-Parts SARL</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Pierre Muller</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-05-15T10:00:00.000Z</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="J2" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Dernier contact","href":null,"text":{"content":"Dernier contact"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Appel téléphonique du 3 juin 2026 avec M. Faber (Agro-Parts SARL). Devis pour 3 kits de joints hydrauliques reçu par email le même jour.","href":null,"text":{"content":"Appel téléphonique du 3 juin 2026 avec M. Faber (Agro-Parts SARL). Devis pour 3 kits de joints hydrauliques reçu par email le même jour."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Actions en cours","href":null,"text":{"content":"Actions en cours"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Devis analysé et validé par le CA le 5 juin – bon de commande en préparation","href":null,"text":{"content":"Devis analysé et validé par le CA le 5 juin – bon de commande en préparation"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Délai de livraison estimé : 10 jours ouvrés","href":null,"text":{"content":"Délai de livraison estimé : 10 jours ouvrés"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Tracteur JD8R maintenu en service réduit en attendant la réparation","href":null,"text":{"content":"Tracteur JD8R maintenu en service réduit en attendant la réparation"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Prochaine étape","href":null,"text":{"content":"Prochaine étape"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Envoyer le bon de commande à Agro-Parts avant le 10 juin. Suivi livraison prévu pour la semaine du 22 juin.","href":null,"text":{"content":"Envoyer le bon de commande à Agro-Parts avant le 10 juin. Suivi livraison prévu pour la semaine du 22 juin."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SV2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Subvention PCAE équipements irrigation</v>
+      </c>
+      <c r="C3" t="str">
+        <v>En attente</v>
+      </c>
+      <c r="D3" t="str">
+        <v>blue</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Lancement produit X</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Sophie Lienhard</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-04-01T09:00:00.000Z</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="J3" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"État du dossier","href":null,"text":{"content":"État du dossier"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Dossier PCAE déposé le 15 avril 2026 auprès de la Chambre d'Agriculture 68. Dossier déclaré complet le 2 mai.","href":null,"text":{"content":"Dossier PCAE déposé le 15 avril 2026 auprès de la Chambre d'Agriculture 68. Dossier déclaré complet le 2 mai."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Documents transmis","href":null,"text":{"content":"Documents transmis"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Attestation d'assurance matériel (transmise le 2 mai)","href":null,"text":{"content":"Attestation d'assurance matériel (transmise le 2 mai)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Devis fournisseur actualisé (reçu le 28 mai, conforme)","href":null,"text":{"content":"Devis fournisseur actualisé (reçu le 28 mai, conforme)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Plan de financement et relevé IBAN CUMA","href":null,"text":{"content":"Plan de financement et relevé IBAN CUMA"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Calendrier prévisionnel","href":null,"text":{"content":"Calendrier prévisionnel"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Instruction dossier : fin juin 2026. Décision préfectorale : avant le 31 juillet. Subvention potentielle : 35 % du coût HT, soit environ 22 750 €.","href":null,"text":{"content":"Instruction dossier : fin juin 2026. Décision préfectorale : avant le 31 juillet. Subvention potentielle : 35 % du coût HT, soit environ 22 750 €."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SV3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Renouvellement parc tracteurs 2026-2027</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Ouvert</v>
+      </c>
+      <c r="D4" t="str">
+        <v>default</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Banque Agricole du Rhin|Agro-Parts SARL</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Marc Zimmermann</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-03-01T09:00:00.000Z</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="J4" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Contexte","href":null,"text":{"content":"Contexte"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Plan pluriannuel de renouvellement : 3 tracteurs à remplacer sur 2 ans. Priorité 2026 : JD8R (12 ans, 9 500 h moteur).","href":null,"text":{"content":"Plan pluriannuel de renouvellement : 3 tracteurs à remplacer sur 2 ans. Priorité 2026 : JD8R (12 ans, 9 500 h moteur)."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Avancement du processus","href":null,"text":{"content":"Avancement du processus"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Comparatif technique réalisé : John Deere 6R 185 vs Fendt 718 Vario","href":null,"text":{"content":"Comparatif technique réalisé : John Deere 6R 185 vs Fendt 718 Vario"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Négociation prix avec concessionnaire Mulhouse : remise de 4 % obtenue","href":null,"text":{"content":"Négociation prix avec concessionnaire Mulhouse : remise de 4 % obtenue"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"numbered_list_item","has_children":false,"numbered_list_item":{"rich_text":[{"type":"text","plain_text":"Vote AG mars 2026 : acquisition JD8R approuvée à 78 % des voix","href":null,"text":{"content":"Vote AG mars 2026 : acquisition JD8R approuvée à 78 % des voix"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Points ouverts","href":null,"text":{"content":"Points ouverts"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Financement : arbitrage crédit-bail 5 ans vs achat comptant (réponse attendue de la BAR)","href":null,"text":{"content":"Financement : arbitrage crédit-bail 5 ans vs achat comptant (réponse attendue de la BAR)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk009","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Reprise ancienne machine : estimation concessionnaire 28 000 € HT","href":null,"text":{"content":"Reprise ancienne machine : estimation concessionnaire 28 000 € HT"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk010","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Budget estimatif","href":null,"text":{"content":"Budget estimatif"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk011","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Nouveau tracteur JD 6R 185 : 145 000 € HT. Après reprise (28 k€) et subvention PCAE (≈ 20 k€) : coût net ≈ 97 000 € HT.","href":null,"text":{"content":"Nouveau tracteur JD 6R 185 : 145 000 € HT. Après reprise (28 k€) et subvention PCAE (≈ 20 k€) : coût net ≈ 97 000 € HT."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SV4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Plan de communication numérique adhérents</v>
+      </c>
+      <c r="C5" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="D5" t="str">
+        <v>green</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Refonte site web</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Coopérative du Grand-Est</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-04-15T14:00:00.000Z</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="J5" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Objectifs","href":null,"text":{"content":"Objectifs"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Moderniser la communication de la CUMA envers ses 235 adhérents : newsletter mensuelle, appli mobile, site web refait.","href":null,"text":{"content":"Moderniser la communication de la CUMA envers ses 235 adhérents : newsletter mensuelle, appli mobile, site web refait."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Décisions prises","href":null,"text":{"content":"Décisions prises"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Newsletter : outil retenu Mailchimp (gratuit jusqu'à 500 contacts)","href":null,"text":{"content":"Newsletter : outil retenu Mailchimp (gratuit jusqu'à 500 contacts)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Appli mobile : développement confié à Alsace Numérique, livraison T3 2026","href":null,"text":{"content":"Appli mobile : développement confié à Alsace Numérique, livraison T3 2026"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Site web : refonte planifiée septembre-octobre 2026","href":null,"text":{"content":"Site web : refonte planifiée septembre-octobre 2026"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Indicateurs à suivre","href":null,"text":{"content":"Indicateurs à suivre"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Cible 80 % d'adhérents avec email d'ici fin 2026. État actuel : 63 % (148/235). Prochain point de suivi : fin juillet 2026.","href":null,"text":{"content":"Cible 80 % d'adhérents avec email d'ici fin 2026. État actuel : 63 % (148/235). Prochain point de suivi : fin juillet 2026."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SV5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Convention partenariat Chambre d'Agriculture 68</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Clôturé</v>
+      </c>
+      <c r="D6" t="str">
+        <v>gray</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Chambre d'Agriculture 68</v>
+      </c>
+      <c r="G6" t="str">
+        <v>André Kessler</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-02-10T09:00:00.000Z</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="J6" t="str">
+        <v>[{"id":"bk001","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Objet de la convention","href":null,"text":{"content":"Objet de la convention"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk002","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Renouvellement de la convention de partenariat avec la Chambre d'Agriculture 68 pour l'accompagnement technique des adhérents de la CUMA.","href":null,"text":{"content":"Renouvellement de la convention de partenariat avec la Chambre d'Agriculture 68 pour l'accompagnement technique des adhérents de la CUMA."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk003","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Termes de la convention signée","href":null,"text":{"content":"Termes de la convention signée"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk004","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Durée : 3 ans (2026-2028)","href":null,"text":{"content":"Durée : 3 ans (2026-2028)"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk005","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Prestations : 2 journées de conseil/an + accès formations Chambre","href":null,"text":{"content":"Prestations : 2 journées de conseil/an + accès formations Chambre"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk006","type":"bulleted_list_item","has_children":false,"bulleted_list_item":{"rich_text":[{"type":"text","plain_text":"Contribution CUMA : 1 500 €/an + mise à disposition de la salle","href":null,"text":{"content":"Contribution CUMA : 1 500 €/an + mise à disposition de la salle"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk007","type":"heading_2","has_children":false,"heading_2":{"rich_text":[{"type":"text","plain_text":"Statut et prochaine échéance","href":null,"text":{"content":"Statut et prochaine échéance"},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}},{"id":"bk008","type":"paragraph","has_children":false,"paragraph":{"rich_text":[{"type":"text","plain_text":"Convention signée le 15 mai 2026. Première prestation planifiée le 18 septembre 2026 : formation irrigation de précision. 12 participants préinscrits.","href":null,"text":{"content":"Convention signée le 15 mai 2026. Première prestation planifiée le 18 septembre 2026 : formation irrigation de précision. 12 participants préinscrits."},"annotations":{"bold":false,"italic":false,"strikethrough":false,"underline":false,"code":false,"color":"default"}}],"color":"default"}}]</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>